--- a/src/test/resources/testdata.xlsx
+++ b/src/test/resources/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prakash\EclipseWorkspace\SeleniumProject\SeleniumIntegration\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159F8A52-F916-4091-940E-4E187A9448A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDD4BC4-B8E9-447C-88E3-7CA7FA53FCF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>Username</t>
   </si>
@@ -67,6 +67,15 @@
   </si>
   <si>
     <t>xpath</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>student4</t>
+  </si>
+  <si>
+    <t>Password45</t>
   </si>
 </sst>
 </file>
@@ -395,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -458,10 +467,28 @@
         <v>11</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{3C6B7772-F00E-4318-9F8D-8E22AAC0871C}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{6133070C-6323-4B7A-9F0C-CE2014931F24}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{2E20EFC0-58AF-4BD4-B46A-BA5E9609174C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
